--- a/tiger_audit_forest_park_pleasant_run/reports/TIGER-Audit-Forest-Park-Pleasant-Run.xlsx
+++ b/tiger_audit_forest_park_pleasant_run/reports/TIGER-Audit-Forest-Park-Pleasant-Run.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T01:57:57+00:00</t>
+          <t>Audit date (UTC): 2026-04-29T02:09:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2270,18 +2270,18 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Holden Boulevard</t>
+          <t>Kolb Drive</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="D15" s="5" t="n">
-        <v>0</v>
+      <c r="D15" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -2296,18 +2296,18 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Kolb Drive</t>
+          <t>Holden Boulevard</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="D16" s="10" t="n">
-        <v>4</v>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -2504,18 +2504,18 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Bent Tree Drive</t>
+          <t>Pictoria Drive</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Kenn Road</t>
+          <t>Wessel Drive</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -2556,18 +2556,18 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Wessel Drive</t>
+          <t>Bent Tree Drive</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D26" s="5" t="n">
-        <v>0</v>
+      <c r="D26" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Ray Norrish Drive</t>
+          <t>Ross Road</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>residential, unclassified</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -2608,18 +2608,18 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Pictoria Drive</t>
+          <t>Kenn Road</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D28" s="10" t="n">
-        <v>5</v>
+      <c r="D28" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Ross Road</t>
+          <t>Pleasant Avenue</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Pleasant Avenue</t>
+          <t>Ray Norrish Drive</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>residential, unclassified</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -2738,14 +2738,14 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Maple Trace</t>
+          <t>Forest Fair Drive</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D33" s="10" t="n">
-        <v>3</v>
+      <c r="D33" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>East Crescentville Road</t>
+          <t>Lawnview Avenue</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -2790,14 +2790,14 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Eswin Street</t>
+          <t>Wildwood Drive</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
@@ -2816,18 +2816,18 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Carillon Boulevard</t>
+          <t>East Crescentville Road</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D36" s="10" t="n">
-        <v>5</v>
+      <c r="D36" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -2842,14 +2842,14 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Lawnview Avenue</t>
+          <t>Carillon Boulevard</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D37" s="5" t="n">
-        <v>0</v>
+      <c r="D37" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
@@ -2868,14 +2868,14 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Forest Fair Drive</t>
+          <t>Eswin Street</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D38" s="5" t="n">
-        <v>0</v>
+      <c r="D38" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
@@ -2894,14 +2894,14 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Wildwood Drive</t>
+          <t>Maple Trace</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
@@ -2920,18 +2920,18 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Commercial Drive</t>
+          <t>South Timber Hollow Drive</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D40" s="5" t="n">
-        <v>0</v>
+      <c r="D40" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Lakeview Drive</t>
+          <t>Commercial Drive</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -2972,18 +2972,18 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>South Timber Hollow Drive</t>
+          <t>Lakeview Drive</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D42" s="10" t="n">
-        <v>1</v>
+      <c r="D42" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Casual Drive</t>
+          <t>Wellesley Place</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Wellesley Place</t>
+          <t>Casual Drive</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
@@ -78580,12 +78580,14 @@
           <t>Blue Ash / Montgomery</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>NOT STARTED</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr"/>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>AUDIT COMPLETE</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>1934</v>
+      </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Blue Ash, Montgomery, Deer Park, Silverton, Kenwood, Madeira</t>
@@ -78598,12 +78600,14 @@
           <t>Springdale / Sharonville</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>NOT STARTED</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr"/>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>AUDIT COMPLETE</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>1549</v>
+      </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Springdale, Sharonville, Glendale, Evendale, Lincoln Heights</t>
@@ -78616,12 +78620,14 @@
           <t>Northgate / Mt. Healthy</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>NOT STARTED</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr"/>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>AUDIT COMPLETE</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>1664</v>
+      </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Mt. Healthy, North College Hill, Finneytown, Northgate</t>
@@ -78845,7 +78851,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T01:57:57+00:00</t>
+          <t>2026-04-29T02:09:57+00:00</t>
         </is>
       </c>
     </row>

--- a/tiger_audit_forest_park_pleasant_run/reports/TIGER-Audit-Forest-Park-Pleasant-Run.xlsx
+++ b/tiger_audit_forest_park_pleasant_run/reports/TIGER-Audit-Forest-Park-Pleasant-Run.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T02:09:57+00:00</t>
+          <t>Audit date (UTC): 2026-04-29T02:18:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Tri-County Parkway</t>
+          <t>Mulhauser Road</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary, tertiary</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Mulhauser Road</t>
+          <t>Tri-County Parkway</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>secondary, tertiary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -2504,18 +2504,18 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Pictoria Drive</t>
+          <t>Kenn Road</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D24" s="10" t="n">
-        <v>5</v>
+      <c r="D24" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -2608,18 +2608,18 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Kenn Road</t>
+          <t>Pictoria Drive</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D28" s="5" t="n">
-        <v>0</v>
+      <c r="D28" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Pleasant Avenue</t>
+          <t>Ray Norrish Drive</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>residential, unclassified</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Ray Norrish Drive</t>
+          <t>Pleasant Avenue</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>residential, unclassified</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -2712,18 +2712,18 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>North Gilmore Road</t>
+          <t>Carillon Boulevard</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D32" s="5" t="n">
-        <v>0</v>
+      <c r="D32" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Forest Fair Drive</t>
+          <t>North Gilmore Road</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -2764,14 +2764,14 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Lawnview Avenue</t>
+          <t>Eswin Street</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D34" s="5" t="n">
-        <v>0</v>
+      <c r="D34" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
@@ -2790,14 +2790,14 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Wildwood Drive</t>
+          <t>Lawnview Avenue</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D35" s="10" t="n">
-        <v>5</v>
+      <c r="D35" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
@@ -2816,18 +2816,18 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>East Crescentville Road</t>
+          <t>Wildwood Drive</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D36" s="5" t="n">
-        <v>0</v>
+      <c r="D36" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -2842,18 +2842,18 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Carillon Boulevard</t>
+          <t>East Crescentville Road</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D37" s="10" t="n">
-        <v>5</v>
+      <c r="D37" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Eswin Street</t>
+          <t>Maple Trace</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
@@ -2894,14 +2894,14 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Maple Trace</t>
+          <t>Forest Fair Drive</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D39" s="10" t="n">
-        <v>3</v>
+      <c r="D39" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
@@ -2920,18 +2920,18 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>South Timber Hollow Drive</t>
+          <t>Commercial Drive</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D40" s="10" t="n">
-        <v>1</v>
+      <c r="D40" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -2946,18 +2946,18 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Commercial Drive</t>
+          <t>South Timber Hollow Drive</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D41" s="5" t="n">
-        <v>0</v>
+      <c r="D41" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -2998,14 +2998,14 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Canal Way</t>
+          <t>Wellesley Place</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D43" s="10" t="n">
-        <v>2</v>
+      <c r="D43" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Wellesley Place</t>
+          <t>Casual Drive</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
@@ -3050,14 +3050,14 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Casual Drive</t>
+          <t>Canal Way</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D45" s="5" t="n">
-        <v>0</v>
+      <c r="D45" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
@@ -78851,7 +78851,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T02:09:57+00:00</t>
+          <t>2026-04-29T02:18:38+00:00</t>
         </is>
       </c>
     </row>

--- a/tiger_audit_forest_park_pleasant_run/reports/TIGER-Audit-Forest-Park-Pleasant-Run.xlsx
+++ b/tiger_audit_forest_park_pleasant_run/reports/TIGER-Audit-Forest-Park-Pleasant-Run.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T02:18:38+00:00</t>
+          <t>Audit date (UTC): 2026-04-29T02:34:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Southland Road</t>
+          <t>Tri-County Parkway</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Mulhauser Road</t>
+          <t>Southland Road</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>secondary, tertiary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Tri-County Parkway</t>
+          <t>Mulhauser Road</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary, tertiary</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Wessel Drive</t>
+          <t>Pleasant Avenue</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -2556,18 +2556,18 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Bent Tree Drive</t>
+          <t>Ross Road</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D26" s="10" t="n">
-        <v>2</v>
+      <c r="D26" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -2582,18 +2582,18 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Ross Road</t>
+          <t>Bent Tree Drive</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D27" s="5" t="n">
-        <v>0</v>
+      <c r="D27" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Ray Norrish Drive</t>
+          <t>Wessel Drive</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>residential, unclassified</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Pleasant Avenue</t>
+          <t>Ray Norrish Drive</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>residential, unclassified</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -2712,14 +2712,14 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Carillon Boulevard</t>
+          <t>Maple Trace</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>North Gilmore Road</t>
+          <t>Lawnview Avenue</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Lawnview Avenue</t>
+          <t>East Crescentville Road</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Wildwood Drive</t>
+          <t>Carillon Boulevard</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>East Crescentville Road</t>
+          <t>Forest Fair Drive</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -2868,18 +2868,18 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Maple Trace</t>
+          <t>North Gilmore Road</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D38" s="10" t="n">
-        <v>3</v>
+      <c r="D38" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -2894,14 +2894,14 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Forest Fair Drive</t>
+          <t>Wildwood Drive</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D39" s="5" t="n">
-        <v>0</v>
+      <c r="D39" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
@@ -2946,18 +2946,18 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>South Timber Hollow Drive</t>
+          <t>Lakeview Drive</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D41" s="10" t="n">
-        <v>1</v>
+      <c r="D41" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -2972,18 +2972,18 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Lakeview Drive</t>
+          <t>South Timber Hollow Drive</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D42" s="5" t="n">
-        <v>0</v>
+      <c r="D42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -3024,14 +3024,14 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Casual Drive</t>
+          <t>Canal Way</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D44" s="5" t="n">
-        <v>0</v>
+      <c r="D44" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
@@ -3050,14 +3050,14 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Canal Way</t>
+          <t>Casual Drive</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D45" s="10" t="n">
-        <v>2</v>
+      <c r="D45" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
@@ -78851,7 +78851,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T02:18:38+00:00</t>
+          <t>2026-04-29T02:34:07+00:00</t>
         </is>
       </c>
     </row>

--- a/tiger_audit_forest_park_pleasant_run/reports/TIGER-Audit-Forest-Park-Pleasant-Run.xlsx
+++ b/tiger_audit_forest_park_pleasant_run/reports/TIGER-Audit-Forest-Park-Pleasant-Run.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T02:34:07+00:00</t>
+          <t>Audit date (UTC): 2026-04-29T02:42:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2270,18 +2270,18 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Kolb Drive</t>
+          <t>Holden Boulevard</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="D15" s="10" t="n">
-        <v>4</v>
+      <c r="D15" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -2296,18 +2296,18 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Holden Boulevard</t>
+          <t>Kolb Drive</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="D16" s="5" t="n">
-        <v>0</v>
+      <c r="D16" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Southland Road</t>
+          <t>Mulhauser Road</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary, tertiary</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Mulhauser Road</t>
+          <t>Southland Road</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>secondary, tertiary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Kenn Road</t>
+          <t>Pleasant Avenue</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Pleasant Avenue</t>
+          <t>Ray Norrish Drive</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>residential, unclassified</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Ross Road</t>
+          <t>Kenn Road</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
@@ -2608,18 +2608,18 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Pictoria Drive</t>
+          <t>Ross Road</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D28" s="10" t="n">
-        <v>5</v>
+      <c r="D28" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -2660,18 +2660,18 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Ray Norrish Drive</t>
+          <t>Pictoria Drive</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D30" s="5" t="n">
-        <v>0</v>
+      <c r="D30" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>residential, unclassified</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -2712,14 +2712,14 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Maple Trace</t>
+          <t>Lawnview Avenue</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D32" s="10" t="n">
-        <v>3</v>
+      <c r="D32" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
@@ -2738,14 +2738,14 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Lawnview Avenue</t>
+          <t>Maple Trace</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D33" s="5" t="n">
-        <v>0</v>
+      <c r="D33" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
@@ -2764,18 +2764,18 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Eswin Street</t>
+          <t>North Gilmore Road</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D34" s="10" t="n">
-        <v>3</v>
+      <c r="D34" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Carillon Boulevard</t>
+          <t>Wildwood Drive</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
@@ -2868,18 +2868,18 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>North Gilmore Road</t>
+          <t>Carillon Boulevard</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D38" s="5" t="n">
-        <v>0</v>
+      <c r="D38" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -2894,14 +2894,14 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Wildwood Drive</t>
+          <t>Eswin Street</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
@@ -2920,18 +2920,18 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Commercial Drive</t>
+          <t>South Timber Hollow Drive</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D40" s="5" t="n">
-        <v>0</v>
+      <c r="D40" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Lakeview Drive</t>
+          <t>Commercial Drive</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -2972,18 +2972,18 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>South Timber Hollow Drive</t>
+          <t>Lakeview Drive</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D42" s="10" t="n">
-        <v>1</v>
+      <c r="D42" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -3024,14 +3024,14 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Canal Way</t>
+          <t>Casual Drive</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D44" s="10" t="n">
-        <v>2</v>
+      <c r="D44" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
@@ -3050,14 +3050,14 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Casual Drive</t>
+          <t>Canal Way</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D45" s="5" t="n">
-        <v>0</v>
+      <c r="D45" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
@@ -78851,7 +78851,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T02:34:07+00:00</t>
+          <t>2026-04-29T02:42:11+00:00</t>
         </is>
       </c>
     </row>

--- a/tiger_audit_forest_park_pleasant_run/reports/TIGER-Audit-Forest-Park-Pleasant-Run.xlsx
+++ b/tiger_audit_forest_park_pleasant_run/reports/TIGER-Audit-Forest-Park-Pleasant-Run.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T02:42:11+00:00</t>
+          <t>Audit date (UTC): 2026-04-29T02:49:22+00:00</t>
         </is>
       </c>
     </row>
@@ -2270,18 +2270,18 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Holden Boulevard</t>
+          <t>Kolb Drive</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="D15" s="5" t="n">
-        <v>0</v>
+      <c r="D15" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -2296,18 +2296,18 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Kolb Drive</t>
+          <t>Holden Boulevard</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="D16" s="10" t="n">
-        <v>4</v>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Tri-County Parkway</t>
+          <t>Southland Road</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Mulhauser Road</t>
+          <t>Tri-County Parkway</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>secondary, tertiary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Southland Road</t>
+          <t>Mulhauser Road</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary, tertiary</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Pleasant Avenue</t>
+          <t>Wessel Drive</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -2556,18 +2556,18 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Kenn Road</t>
+          <t>Pictoria Drive</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D26" s="5" t="n">
-        <v>0</v>
+      <c r="D26" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Ross Road</t>
+          <t>Kenn Road</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Wessel Drive</t>
+          <t>Ross Road</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2660,18 +2660,18 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Pictoria Drive</t>
+          <t>Pleasant Avenue</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D30" s="10" t="n">
-        <v>5</v>
+      <c r="D30" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -2712,14 +2712,14 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Lawnview Avenue</t>
+          <t>Eswin Street</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D32" s="5" t="n">
-        <v>0</v>
+      <c r="D32" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
@@ -2738,14 +2738,14 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Maple Trace</t>
+          <t>Wildwood Drive</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>North Gilmore Road</t>
+          <t>East Crescentville Road</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
@@ -2790,18 +2790,18 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>East Crescentville Road</t>
+          <t>Carillon Boulevard</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D35" s="5" t="n">
-        <v>0</v>
+      <c r="D35" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -2816,14 +2816,14 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Wildwood Drive</t>
+          <t>Maple Trace</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
@@ -2868,14 +2868,14 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Carillon Boulevard</t>
+          <t>Lawnview Avenue</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D38" s="10" t="n">
-        <v>5</v>
+      <c r="D38" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
@@ -2894,18 +2894,18 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Eswin Street</t>
+          <t>North Gilmore Road</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D39" s="10" t="n">
-        <v>3</v>
+      <c r="D39" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -2920,18 +2920,18 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>South Timber Hollow Drive</t>
+          <t>Lakeview Drive</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D40" s="10" t="n">
-        <v>1</v>
+      <c r="D40" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -2946,18 +2946,18 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Commercial Drive</t>
+          <t>South Timber Hollow Drive</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D41" s="5" t="n">
-        <v>0</v>
+      <c r="D41" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Lakeview Drive</t>
+          <t>Commercial Drive</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -2998,14 +2998,14 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Wellesley Place</t>
+          <t>Canal Way</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D43" s="5" t="n">
-        <v>0</v>
+      <c r="D43" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
@@ -3050,14 +3050,14 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Canal Way</t>
+          <t>Wellesley Place</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D45" s="10" t="n">
-        <v>2</v>
+      <c r="D45" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
@@ -78851,7 +78851,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T02:42:11+00:00</t>
+          <t>2026-04-29T02:49:22+00:00</t>
         </is>
       </c>
     </row>

--- a/tiger_audit_forest_park_pleasant_run/reports/TIGER-Audit-Forest-Park-Pleasant-Run.xlsx
+++ b/tiger_audit_forest_park_pleasant_run/reports/TIGER-Audit-Forest-Park-Pleasant-Run.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T02:49:22+00:00</t>
+          <t>Audit date (UTC): 2026-04-29T13:08:03+00:00</t>
         </is>
       </c>
     </row>
@@ -2270,18 +2270,18 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Kolb Drive</t>
+          <t>Holden Boulevard</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="D15" s="10" t="n">
-        <v>4</v>
+      <c r="D15" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -2296,18 +2296,18 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Holden Boulevard</t>
+          <t>Kolb Drive</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="D16" s="5" t="n">
-        <v>0</v>
+      <c r="D16" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Southland Road</t>
+          <t>Tri-County Parkway</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Tri-County Parkway</t>
+          <t>Southland Road</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Wessel Drive</t>
+          <t>Ross Road</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Ray Norrish Drive</t>
+          <t>Pleasant Avenue</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>residential, unclassified</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -2556,18 +2556,18 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Pictoria Drive</t>
+          <t>Ray Norrish Drive</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D26" s="10" t="n">
-        <v>5</v>
+      <c r="D26" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>residential, unclassified</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -2582,18 +2582,18 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Bent Tree Drive</t>
+          <t>Wessel Drive</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D27" s="10" t="n">
-        <v>2</v>
+      <c r="D27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -2634,18 +2634,18 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Ross Road</t>
+          <t>Pictoria Drive</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D29" s="5" t="n">
-        <v>0</v>
+      <c r="D29" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2660,18 +2660,18 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Pleasant Avenue</t>
+          <t>Bent Tree Drive</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D30" s="5" t="n">
-        <v>0</v>
+      <c r="D30" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -2712,14 +2712,14 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Eswin Street</t>
+          <t>Lawnview Avenue</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D32" s="10" t="n">
-        <v>3</v>
+      <c r="D32" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
@@ -2738,14 +2738,14 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Wildwood Drive</t>
+          <t>Maple Trace</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>East Crescentville Road</t>
+          <t>Forest Fair Drive</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -2790,18 +2790,18 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Carillon Boulevard</t>
+          <t>North Gilmore Road</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D35" s="10" t="n">
-        <v>5</v>
+      <c r="D35" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -2816,14 +2816,14 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Maple Trace</t>
+          <t>Carillon Boulevard</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
@@ -2842,14 +2842,14 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Forest Fair Drive</t>
+          <t>Wildwood Drive</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D37" s="5" t="n">
-        <v>0</v>
+      <c r="D37" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
@@ -2868,14 +2868,14 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Lawnview Avenue</t>
+          <t>Eswin Street</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D38" s="5" t="n">
-        <v>0</v>
+      <c r="D38" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>North Gilmore Road</t>
+          <t>East Crescentville Road</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
@@ -2998,14 +2998,14 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Canal Way</t>
+          <t>Casual Drive</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D43" s="10" t="n">
-        <v>2</v>
+      <c r="D43" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
@@ -3024,14 +3024,14 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Casual Drive</t>
+          <t>Canal Way</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D44" s="5" t="n">
-        <v>0</v>
+      <c r="D44" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
@@ -78851,7 +78851,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T02:49:22+00:00</t>
+          <t>2026-04-29T13:08:03+00:00</t>
         </is>
       </c>
     </row>

--- a/tiger_audit_forest_park_pleasant_run/reports/TIGER-Audit-Forest-Park-Pleasant-Run.xlsx
+++ b/tiger_audit_forest_park_pleasant_run/reports/TIGER-Audit-Forest-Park-Pleasant-Run.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T13:08:03+00:00</t>
+          <t>Audit date (UTC): 2026-04-30T17:05:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2270,18 +2270,18 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Holden Boulevard</t>
+          <t>Kolb Drive</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="D15" s="5" t="n">
-        <v>0</v>
+      <c r="D15" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -2296,18 +2296,18 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Kolb Drive</t>
+          <t>Holden Boulevard</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="D16" s="10" t="n">
-        <v>4</v>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -2504,18 +2504,18 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Ross Road</t>
+          <t>Bent Tree Drive</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D24" s="5" t="n">
-        <v>0</v>
+      <c r="D24" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential, service</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -2530,18 +2530,18 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Pleasant Avenue</t>
+          <t>Pictoria Drive</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D25" s="5" t="n">
-        <v>0</v>
+      <c r="D25" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Ray Norrish Drive</t>
+          <t>Wessel Drive</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>residential, unclassified</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Wessel Drive</t>
+          <t>Pleasant Avenue</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Kenn Road</t>
+          <t>Ross Road</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
@@ -2634,18 +2634,18 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Pictoria Drive</t>
+          <t>Ray Norrish Drive</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D29" s="10" t="n">
-        <v>5</v>
+      <c r="D29" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>residential, unclassified</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2660,18 +2660,18 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Bent Tree Drive</t>
+          <t>Kenn Road</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D30" s="10" t="n">
-        <v>2</v>
+      <c r="D30" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>residential, service</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Lawnview Avenue</t>
+          <t>North Gilmore Road</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Maple Trace</t>
+          <t>Eswin Street</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
@@ -2764,14 +2764,14 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Forest Fair Drive</t>
+          <t>Carillon Boulevard</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D34" s="5" t="n">
-        <v>0</v>
+      <c r="D34" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>North Gilmore Road</t>
+          <t>Lawnview Avenue</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -2816,14 +2816,14 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Carillon Boulevard</t>
+          <t>Forest Fair Drive</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D36" s="10" t="n">
-        <v>5</v>
+      <c r="D36" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
@@ -2842,18 +2842,18 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Wildwood Drive</t>
+          <t>East Crescentville Road</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D37" s="10" t="n">
-        <v>5</v>
+      <c r="D37" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Eswin Street</t>
+          <t>Maple Trace</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
@@ -2894,18 +2894,18 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>East Crescentville Road</t>
+          <t>Wildwood Drive</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D39" s="5" t="n">
-        <v>0</v>
+      <c r="D39" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Lakeview Drive</t>
+          <t>Commercial Drive</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Commercial Drive</t>
+          <t>Lakeview Drive</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Casual Drive</t>
+          <t>Wellesley Place</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
@@ -3024,14 +3024,14 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Canal Way</t>
+          <t>Casual Drive</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D44" s="10" t="n">
-        <v>2</v>
+      <c r="D44" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
@@ -3050,14 +3050,14 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Wellesley Place</t>
+          <t>Canal Way</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D45" s="5" t="n">
-        <v>0</v>
+      <c r="D45" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
@@ -78851,7 +78851,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T13:08:03+00:00</t>
+          <t>2026-04-30T17:05:38+00:00</t>
         </is>
       </c>
     </row>
